--- a/plc_log_lists.xlsx
+++ b/plc_log_lists.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\elecroomscada_mariadb\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mariadbelecroomscada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C588AD0-BE37-4D6D-BFFB-B1A571690F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FA319D-3AC1-49F1-884F-C393AAB7A8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40380" yWindow="3990" windowWidth="17370" windowHeight="11910" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
+    <workbookView xWindow="-27510" yWindow="1605" windowWidth="23415" windowHeight="11295" activeTab="1" xr2:uid="{11B8FF3D-C01C-4713-9E37-34D18F872282}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="89">
   <si>
     <t>D0006420.9</t>
   </si>
@@ -188,6 +189,127 @@
   </si>
   <si>
     <t>배기팬 가동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>변압기 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터크기 (word)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>읽을주소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>변압기 2</t>
+  </si>
+  <si>
+    <t>변압기 3</t>
+  </si>
+  <si>
+    <t>0x30004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모드버스 RTU 클라이언트</t>
+  </si>
+  <si>
+    <t>READ</t>
+  </si>
+  <si>
+    <t>_T1S</t>
+  </si>
+  <si>
+    <t>2. 연속</t>
+  </si>
+  <si>
+    <t>WORD</t>
+  </si>
+  <si>
+    <t>개수:1\nREAD1:0x30004,SAVE1:D00500\n</t>
+  </si>
+  <si>
+    <t>개수:1\nREAD1:0x30004,SAVE1:D00600\n</t>
+  </si>
+  <si>
+    <t>개수:1\nREAD1:0x30004,SAVE1:D00700\n</t>
+  </si>
+  <si>
+    <t>개수:1\nREAD1:0x303E8,SAVE1:D06518\n</t>
+  </si>
+  <si>
+    <t>WRITE</t>
+  </si>
+  <si>
+    <t>1. 개별</t>
+  </si>
+  <si>
+    <t>개수:1\nREAD1:D06629,SAVE1:0x40000\n</t>
+  </si>
+  <si>
+    <t>개수:1\nREAD1:D06641,SAVE1:0x40035\n</t>
+  </si>
+  <si>
+    <t>D06506.F</t>
+  </si>
+  <si>
+    <t>개수:1\nREAD1:D00900,SAVE1:0x40000\n</t>
+  </si>
+  <si>
+    <t>개수:1\nREAD1:0x30004,SAVE1:D00400\n</t>
+  </si>
+  <si>
+    <t>개수:1\nREAD1:0x30000,SAVE1:D02000\n</t>
+  </si>
+  <si>
+    <t>채널</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설정드라이버</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P2P 기능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기동 조건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터 타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>변수 개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터크기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상대국번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>변수 설정내용</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -553,12 +675,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F39EDAB4-4F9F-43D7-A646-D97796DCEFC3}">
   <dimension ref="B2:G21"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -578,7 +700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -598,7 +720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -618,7 +740,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -638,7 +760,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>12</v>
       </c>
@@ -658,7 +780,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>14</v>
       </c>
@@ -678,7 +800,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -698,7 +820,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>20</v>
       </c>
@@ -718,7 +840,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>23</v>
       </c>
@@ -738,7 +860,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>26</v>
       </c>
@@ -758,7 +880,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>29</v>
       </c>
@@ -778,7 +900,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>31</v>
       </c>
@@ -798,7 +920,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>34</v>
       </c>
@@ -818,7 +940,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>37</v>
       </c>
@@ -838,7 +960,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>40</v>
       </c>
@@ -858,7 +980,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>43</v>
       </c>
@@ -878,7 +1000,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>46</v>
       </c>
@@ -898,7 +1020,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>49</v>
       </c>
@@ -916,6 +1038,425 @@
       </c>
       <c r="G21" t="s">
         <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8080AFF7-3269-4242-B7CC-60847005EB76}">
+  <dimension ref="A1:U10"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="11" max="11" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="40.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L1" t="s">
+        <v>80</v>
+      </c>
+      <c r="M1" t="s">
+        <v>81</v>
+      </c>
+      <c r="N1" t="s">
+        <v>82</v>
+      </c>
+      <c r="O1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>85</v>
+      </c>
+      <c r="R1" t="s">
+        <v>86</v>
+      </c>
+      <c r="T1" t="s">
+        <v>87</v>
+      </c>
+      <c r="U1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>38</v>
+      </c>
+      <c r="E2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P2" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>38</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>38</v>
+      </c>
+      <c r="E3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3" t="s">
+        <v>63</v>
+      </c>
+      <c r="N3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O3" t="s">
+        <v>65</v>
+      </c>
+      <c r="P3" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>38</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>2</v>
+      </c>
+      <c r="U3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>38</v>
+      </c>
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M4" t="s">
+        <v>63</v>
+      </c>
+      <c r="N4" t="s">
+        <v>64</v>
+      </c>
+      <c r="O4" t="s">
+        <v>65</v>
+      </c>
+      <c r="P4" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>38</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>3</v>
+      </c>
+      <c r="U4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>52</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5" t="s">
+        <v>62</v>
+      </c>
+      <c r="M5" t="s">
+        <v>63</v>
+      </c>
+      <c r="N5" t="s">
+        <v>64</v>
+      </c>
+      <c r="O5" t="s">
+        <v>65</v>
+      </c>
+      <c r="P5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>4</v>
+      </c>
+      <c r="U5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6" t="s">
+        <v>62</v>
+      </c>
+      <c r="M6" t="s">
+        <v>71</v>
+      </c>
+      <c r="N6" t="s">
+        <v>64</v>
+      </c>
+      <c r="O6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>4</v>
+      </c>
+      <c r="U6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7" t="s">
+        <v>62</v>
+      </c>
+      <c r="M7" t="s">
+        <v>71</v>
+      </c>
+      <c r="N7" t="s">
+        <v>64</v>
+      </c>
+      <c r="O7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P7" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>4</v>
+      </c>
+      <c r="U7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" t="s">
+        <v>71</v>
+      </c>
+      <c r="N8" t="s">
+        <v>75</v>
+      </c>
+      <c r="O8" t="s">
+        <v>65</v>
+      </c>
+      <c r="P8" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>52</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>5</v>
+      </c>
+      <c r="U8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9" t="s">
+        <v>63</v>
+      </c>
+      <c r="N9" t="s">
+        <v>64</v>
+      </c>
+      <c r="O9" t="s">
+        <v>65</v>
+      </c>
+      <c r="P9" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>32</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>6</v>
+      </c>
+      <c r="U9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10" t="s">
+        <v>62</v>
+      </c>
+      <c r="M10" t="s">
+        <v>63</v>
+      </c>
+      <c r="N10" t="s">
+        <v>64</v>
+      </c>
+      <c r="O10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>2</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>5</v>
+      </c>
+      <c r="U10" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
